--- a/data/trans_camb/IQ2605_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IQ2605_R2-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32,2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,42</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>33,36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,2</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 24,66</t>
+          <t>-0,25; 30,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,09; 47,01</t>
+          <t>17,04; 45,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 24,89</t>
+          <t>-23,91; 21,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 29,63</t>
+          <t>-5,42; 26,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,85; 46,08</t>
+          <t>18,88; 47,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 24,03</t>
+          <t>-24,47; 24,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 23,11</t>
+          <t>0,69; 22,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,3; 42,57</t>
+          <t>22,2; 41,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 16,31</t>
+          <t>-16,71; 16,54</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-3,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>20,75%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>72,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34,26%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>76,82%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>-2,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>-3,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 64,26</t>
+          <t>-0,53; 95,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,04; 127,96</t>
+          <t>34,02; 138,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 61,13</t>
+          <t>-49,69; 60,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 89,46</t>
+          <t>-10,45; 73,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,55; 141,36</t>
+          <t>34,21; 130,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 66,47</t>
+          <t>-49,53; 62,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 59,98</t>
+          <t>2,26; 59,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,57; 112,44</t>
+          <t>44,24; 111,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 40,41</t>
+          <t>-36,16; 43,1</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25,94</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>33,56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>40,79</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29,75</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>43,77</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,23</t>
+          <t>11,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22,71</t>
+          <t>19,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,07; 43,77</t>
+          <t>19,78; 40,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,53; 50,71</t>
+          <t>34,21; 52,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 36,89</t>
+          <t>7,47; 41,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,85; 39,52</t>
+          <t>22,08; 44,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,22; 52,21</t>
+          <t>30,23; 50,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 44,93</t>
+          <t>-8,78; 30,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,27; 38,97</t>
+          <t>24,21; 38,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,73; 48,97</t>
+          <t>35,74; 49,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 35,64</t>
+          <t>5,23; 33,33</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>71,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>86,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35,76%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>68,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,38; 108,67</t>
+          <t>40,11; 110,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,34; 129,23</t>
+          <t>67,93; 142,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 87,18</t>
+          <t>17,3; 109,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,48; 108,89</t>
+          <t>40,91; 110,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,95; 141,94</t>
+          <t>55,33; 127,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,35; 116,09</t>
+          <t>-16,97; 70,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,13; 95,96</t>
+          <t>49,1; 96,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>72,11; 121,75</t>
+          <t>72,95; 123,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 84,83</t>
+          <t>10,26; 77,86</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>42,97</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33,1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>37,61</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,01</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,9</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>42,97</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,93</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,11</t>
+          <t>18,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>25,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,26; 48,79</t>
+          <t>30,02; 53,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 17,02</t>
+          <t>9,37; 37,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 36,13</t>
+          <t>11,28; 50,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,53; 54,53</t>
+          <t>25,17; 48,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 36,79</t>
+          <t>-12,76; 16,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 54,02</t>
+          <t>-0,26; 37,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,8; 49,11</t>
+          <t>32,3; 48,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 23,5</t>
+          <t>3,66; 23,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,84; 39,74</t>
+          <t>11,6; 40,1</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107,75%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60,01%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>82,99%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>73,68%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3,93%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37,03%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>107,75%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>60,01%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,27; 118,24</t>
+          <t>64,67; 166,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 39,25</t>
+          <t>20,13; 113,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 81,5</t>
+          <t>31,98; 157,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66,74; 166,73</t>
+          <t>42,09; 117,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,13; 115,79</t>
+          <t>-23,7; 38,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,23; 161,08</t>
+          <t>0,13; 84,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,36; 127,48</t>
+          <t>64,76; 126,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 57,43</t>
+          <t>6,93; 57,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,98; 98,06</t>
+          <t>25,07; 100,81</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27,35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35,86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35,87</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>30,86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>28,02</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-17,94</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27,35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35,86</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,19</t>
+          <t>-17,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>4,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,57; 40,66</t>
+          <t>16,51; 39,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,61; 39,15</t>
+          <t>24,97; 46,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 6,68</t>
+          <t>11,27; 50,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,3; 38,31</t>
+          <t>19,5; 41,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,44; 45,78</t>
+          <t>16,5; 39,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 48,47</t>
+          <t>-39,46; 9,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,27; 37,41</t>
+          <t>21,03; 37,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,25; 40,08</t>
+          <t>23,61; 39,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 22,6</t>
+          <t>-18,09; 23,69</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>50,74%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>66,53%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>66,54%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>56,62%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>51,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-32,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>50,74%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>66,53%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>-31,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,95; 88,13</t>
+          <t>26,73; 87,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,38; 83,63</t>
+          <t>40,7; 101,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 12,73</t>
+          <t>22,14; 107,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,57; 84,29</t>
+          <t>32,75; 88,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,15; 100,85</t>
+          <t>27,62; 87,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,93; 104,72</t>
+          <t>-68,58; 18,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,89; 77,28</t>
+          <t>35,49; 77,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,31; 81,76</t>
+          <t>39,09; 82,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 45,94</t>
+          <t>-30,91; 47,09</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27,96</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>25,99</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,72</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>35,62</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>33,99</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,83</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>27,96</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>34,73</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>30,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 18,59</t>
+          <t>-20,4; 13,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,09; 50,16</t>
+          <t>14,7; 41,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,62; 51,21</t>
+          <t>5,71; 39,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 14,0</t>
+          <t>-17,04; 18,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,88; 40,67</t>
+          <t>21,37; 49,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,82; 41,82</t>
+          <t>13,67; 50,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 11,28</t>
+          <t>-12,71; 11,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,56; 40,49</t>
+          <t>20,59; 42,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17,51; 42,81</t>
+          <t>16,31; 41,49</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,37%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>43,2%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40,14%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3,23%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>67,02%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>63,96%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-4,37%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43,2%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 43,56</t>
+          <t>-27,83; 23,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,75; 120,44</t>
+          <t>19,44; 76,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22,66; 121,11</t>
+          <t>10,17; 73,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 24,17</t>
+          <t>-28,2; 41,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,26; 77,61</t>
+          <t>34,96; 120,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,83; 76,66</t>
+          <t>23,42; 121,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 21,66</t>
+          <t>-19,48; 21,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32,4; 79,1</t>
+          <t>30,41; 83,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,01; 83,44</t>
+          <t>26,39; 79,67</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>35,88</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25,86</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>35,98</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>39,13</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>24,79</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>42,01</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>35,88</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>25,86</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,82</t>
+          <t>42,91</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>39,31</t>
+          <t>39,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>23,58; 52,84</t>
+          <t>22,54; 48,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10,46; 40,82</t>
+          <t>11,91; 41,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,5; 61,38</t>
+          <t>11,93; 51,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23,31; 48,98</t>
+          <t>24,57; 52,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,17; 40,13</t>
+          <t>9,58; 38,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,32; 50,92</t>
+          <t>14,64; 61,27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,15; 46,31</t>
+          <t>27,93; 47,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15,01; 35,95</t>
+          <t>14,49; 35,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24,27; 51,22</t>
+          <t>23,54; 50,8</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>55,5%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>77,2%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>94,07%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>59,59%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>101,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>77,0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>55,5%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>103,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>46,33; 165,85</t>
+          <t>40,37; 129,27</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19,94; 126,49</t>
+          <t>22,29; 106,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>38,25; 177,05</t>
+          <t>23,28; 130,26</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43,2; 134,33</t>
+          <t>49,92; 164,99</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19,21; 104,47</t>
+          <t>20,05; 119,24</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,15; 135,71</t>
+          <t>36,2; 183,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,65; 122,96</t>
+          <t>54,44; 123,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>29,82; 94,13</t>
+          <t>29,75; 93,09</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50,27; 131,77</t>
+          <t>48,97; 130,54</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>18,76</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>13,46</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>21,29</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>15,88</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>12,88</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>26,18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>18,76</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>13,46</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,02</t>
+          <t>25,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,16</t>
+          <t>22,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,21; 25,3</t>
+          <t>9,03; 26,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,65; 23,1</t>
+          <t>3,1; 22,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,97; 39,41</t>
+          <t>7,4; 36,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,78; 28,03</t>
+          <t>5,41; 24,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,3; 22,57</t>
+          <t>3,2; 22,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,74; 35,27</t>
+          <t>8,05; 38,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,68; 24,05</t>
+          <t>10,34; 24,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,96; 19,69</t>
+          <t>6,44; 20,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,15; 32,53</t>
+          <t>11,55; 32,36</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>35,29%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>40,04%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>30,53%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>24,75%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>35,29%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>25,33%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>8,78; 54,09</t>
+          <t>15,8; 56,84</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,63; 49,69</t>
+          <t>5,12; 46,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,19; 83,4</t>
+          <t>13,51; 73,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,35; 59,69</t>
+          <t>9,69; 52,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,78; 47,76</t>
+          <t>5,65; 47,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,87; 72,62</t>
+          <t>15,84; 82,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,31; 49,32</t>
+          <t>18,46; 50,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>12,49; 40,19</t>
+          <t>11,21; 42,66</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>20,94; 65,62</t>
+          <t>21,38; 65,69</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>6,03</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>19,72</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>23,77</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>3,42</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>14,3</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>29,17</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>6,03</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>19,72</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,03</t>
+          <t>28,66</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25,89</t>
+          <t>25,54</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 12,0</t>
+          <t>-2,53; 13,97</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,57; 22,56</t>
+          <t>12,36; 26,52</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>18,73; 35,24</t>
+          <t>12,26; 32,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 15,01</t>
+          <t>-4,86; 11,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,81; 27,07</t>
+          <t>7,28; 22,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,76; 32,29</t>
+          <t>16,61; 35,52</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 10,7</t>
+          <t>-1,21; 10,75</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>11,6; 22,02</t>
+          <t>11,85; 22,67</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18,4; 31,74</t>
+          <t>17,58; 31,7</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>20,97%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>29,66%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 18,73</t>
+          <t>-3,56; 22,99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9,08; 35,78</t>
+          <t>17,5; 42,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26,9; 56,48</t>
+          <t>17,89; 53,4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 24,5</t>
+          <t>-6,78; 18,16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>18,96; 44,51</t>
+          <t>10,28; 36,6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,87; 52,77</t>
+          <t>24,26; 56,37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 16,23</t>
+          <t>-1,57; 17,04</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>16,52; 34,75</t>
+          <t>16,77; 35,51</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>26,53; 49,23</t>
+          <t>26,38; 50,3</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>20,39</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>26,33</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>23,5</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>19,66</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>22,07</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>17,97</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>20,39</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>26,33</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,52</t>
+          <t>17,28</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>21,08</t>
+          <t>20,72</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>15,42; 23,83</t>
+          <t>16,46; 23,92</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>18,16; 26,21</t>
+          <t>22,41; 29,82</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11,12; 24,55</t>
+          <t>16,5; 29,61</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15,86; 24,16</t>
+          <t>14,95; 23,58</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>21,8; 30,24</t>
+          <t>17,88; 25,94</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,6; 29,91</t>
+          <t>10,04; 24,29</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,24; 23,07</t>
+          <t>17,28; 23,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>21,38; 27,05</t>
+          <t>21,7; 27,12</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16,78; 25,71</t>
+          <t>15,52; 25,44</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>49,83%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>36,43%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>40,9%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>38,58%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>27,33; 46,42</t>
+          <t>29,64; 47,61</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>31,96; 51,59</t>
+          <t>40,71; 59,33</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>20,07; 46,64</t>
+          <t>30,52; 57,89</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>28,42; 48,02</t>
+          <t>26,63; 46,15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>39,74; 59,9</t>
+          <t>31,9; 50,8</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>31,1; 58,53</t>
+          <t>18,31; 46,55</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>31,49; 44,79</t>
+          <t>31,36; 44,54</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>38,5; 52,0</t>
+          <t>39,46; 52,87</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>30,61; 49,25</t>
+          <t>28,4; 49,1</t>
         </is>
       </c>
     </row>
